--- a/clean data/goldata.xlsx
+++ b/clean data/goldata.xlsx
@@ -683,7 +683,7 @@
         <v>45261</v>
       </c>
       <c r="C23" t="n">
-        <v>124345.9</v>
+        <v>62173</v>
       </c>
     </row>
     <row r="24">
@@ -694,7 +694,7 @@
         <v>45231</v>
       </c>
       <c r="C24" t="n">
-        <v>121571.9</v>
+        <v>60786.12</v>
       </c>
     </row>
     <row r="25">
@@ -705,7 +705,7 @@
         <v>45200</v>
       </c>
       <c r="C25" t="n">
-        <v>117546.4</v>
+        <v>58773</v>
       </c>
     </row>
     <row r="26">
@@ -716,7 +716,7 @@
         <v>45170</v>
       </c>
       <c r="C26" t="n">
-        <v>117485</v>
+        <v>58743.45</v>
       </c>
     </row>
     <row r="27">
@@ -727,7 +727,7 @@
         <v>45139</v>
       </c>
       <c r="C27" t="n">
-        <v>117475.9</v>
+        <v>58738.31</v>
       </c>
     </row>
     <row r="28">
@@ -738,7 +738,7 @@
         <v>45108</v>
       </c>
       <c r="C28" t="n">
-        <v>117843.42</v>
+        <v>58922.09</v>
       </c>
     </row>
     <row r="29">
@@ -749,7 +749,7 @@
         <v>45078</v>
       </c>
       <c r="C29" t="n">
-        <v>118112.76</v>
+        <v>59056.12</v>
       </c>
     </row>
     <row r="30">
@@ -760,7 +760,7 @@
         <v>45047</v>
       </c>
       <c r="C30" t="n">
-        <v>121165.54</v>
+        <v>60583</v>
       </c>
     </row>
     <row r="31">
@@ -771,7 +771,7 @@
         <v>45017</v>
       </c>
       <c r="C31" t="n">
-        <v>120290.48</v>
+        <v>60145.25</v>
       </c>
     </row>
     <row r="32">
@@ -782,7 +782,7 @@
         <v>44986</v>
       </c>
       <c r="C32" t="n">
-        <v>115027.34</v>
+        <v>57514</v>
       </c>
     </row>
     <row r="33">
@@ -793,7 +793,7 @@
         <v>44958</v>
       </c>
       <c r="C33" t="n">
-        <v>113291.2</v>
+        <v>56646</v>
       </c>
     </row>
     <row r="34">
@@ -804,7 +804,7 @@
         <v>44927</v>
       </c>
       <c r="C34" t="n">
-        <v>112492.66</v>
+        <v>56246.1</v>
       </c>
     </row>
     <row r="35">
